--- a/HARDWARE/BOM_GNSS_Alarm_Clock_v2_digikey.xlsx
+++ b/HARDWARE/BOM_GNSS_Alarm_Clock_v2_digikey.xlsx
@@ -60,7 +60,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
         <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +98,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -128,6 +133,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,15 +387,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55.64" customWidth="1" style="5" min="1" max="1"/>
     <col width="6" customWidth="1" style="5" min="2" max="2"/>
     <col width="30.64" customWidth="1" style="5" min="3" max="3"/>
     <col width="34" customWidth="1" style="5" min="4" max="4"/>
-    <col width="20" customWidth="1" style="5" min="5" max="5"/>
-    <col width="110.67" customWidth="1" style="5" min="6" max="6"/>
+    <col width="15" customWidth="1" style="5" min="5" max="5"/>
+    <col width="34" customWidth="1" style="5" min="6" max="6"/>
+    <col width="66" customWidth="1" style="6" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="6">
@@ -406,6 +413,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="6">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -427,12 +435,17 @@
           <t>Price</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Line total (NOK)</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Digikey Partnumber</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -455,12 +468,16 @@
       <c r="D5" s="10" t="n">
         <v>2.99</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10">
+        <f>IFERROR(B5*D5,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1276-CL21A226MAYNNNECT-ND</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Samsung CL21A226MAYNNNE. BACKORDER: 0 pa lager, paafyll ~15-09-2026 (22uF/0805 bredt restordret)</t>
         </is>
@@ -483,12 +500,16 @@
       <c r="D6" s="10" t="n">
         <v>1.54</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="10">
+        <f>IFERROR(B6*D6,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>399-C0805C105K3RACTUCT-ND</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>KEMET C0805C105K3RACTU</t>
         </is>
@@ -511,12 +532,16 @@
       <c r="D7" s="10" t="n">
         <v>2.22</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="10">
+        <f>IFERROR(B7*D7,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>445-7644-1-ND</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>TDK C2012X5R1C106K085AC (905 pa lager - nok til 14 stk)</t>
         </is>
@@ -539,12 +564,16 @@
       <c r="D8" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="10">
+        <f>IFERROR(B8*D8,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>445-4116-1-ND</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>TDK C2012X5R1E475K125AB</t>
         </is>
@@ -567,12 +596,16 @@
       <c r="D9" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="10">
+        <f>IFERROR(B9*D9,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1276-1003-1-ND</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Samsung CL21B104KBCNNNC</t>
         </is>
@@ -595,12 +628,16 @@
       <c r="D10" s="10" t="n">
         <v>7.72</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="10">
+        <f>IFERROR(B10*D10,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>P15084CT-ND</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Bulk electrolytic - polymer upgrade candidate (e.g. Nichicon RSA series), 10V rating for the VSYS-side position. | Panasonic EEE-FT1A221AP (elko). Polymer-alternativ: Nichicon RSA0J331MCN1GS = 493-7370-1-ND, 10,61 kr, god lagerstatus</t>
         </is>
@@ -623,12 +660,16 @@
       <c r="D11" s="10" t="n">
         <v>1.06</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="10">
+        <f>IFERROR(B11*D11,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>732-7846-1-ND</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Wurth 885012007051 (Samsung-originalen utgatt)</t>
         </is>
@@ -651,12 +692,16 @@
       <c r="D12" s="10" t="n">
         <v>12.25</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="10">
+        <f>IFERROR(B12*D12,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>2073-USB4110-GF-A-1-ND</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
     </row>
     <row r="13" ht="16.4" customHeight="1" s="6">
       <c r="A13" s="9" t="inlineStr">
@@ -675,12 +720,16 @@
       <c r="D13" s="10" t="n">
         <v>5.69</v>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="10">
+        <f>IFERROR(B13*D13,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1175-1627-ND</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>CNC Tech 3220-10-0100-00</t>
         </is>
@@ -703,12 +752,16 @@
       <c r="D14" s="10" t="n">
         <v>2.89</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="10">
+        <f>IFERROR(B14*D14,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1651049</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
     </row>
     <row r="15" ht="16.4" customHeight="1" s="6">
       <c r="A15" s="9" t="inlineStr">
@@ -727,12 +780,16 @@
       <c r="D15" s="10" t="n">
         <v>1.06</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="10">
+        <f>IFERROR(B15*D15,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>926611</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Battery connector - production cell: 505060 LiPo 3.7V 2000mAh with PCM. | pris per stk</t>
         </is>
@@ -755,12 +812,16 @@
       <c r="D16" s="10" t="n">
         <v>5.21</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="10">
+        <f>IFERROR(B16*D16,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>445-VLCF4020T-2R2N1R7CT-ND</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>TDK. BACKORDER: paafyll ~03-09-2026</t>
         </is>
@@ -783,12 +844,16 @@
       <c r="D17" s="10" t="n">
         <v>4.15</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="10">
+        <f>IFERROR(B17*D17,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>445-6683-1-ND</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>EQUIVALENT: TDK VLS4012ET-1R0N for YXMAA0412-1R0M (1uH 4x4x1.2mm 2.5A) - NB: NRND</t>
         </is>
@@ -811,12 +876,16 @@
       <c r="D18" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="10">
+        <f>IFERROR(B18*D18,"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>490-LQH32CN100K33LCT-ND</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>EQUIVALENT: Murata LQH32CN100K33L 1210 (LQH31CN utgatt, dette er Muratas erstatning)</t>
         </is>
@@ -839,12 +908,16 @@
       <c r="D19" s="10" t="n">
         <v>3.86</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="10">
+        <f>IFERROR(B19*D19,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>160-1725-1-ND</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>ADVARSEL: OR-PL020W er en SIDE-EMITTER 3.8x1.2mm (LCSC-datablad) - LTW-670DS (PLCC-2 toppemitter) er FEIL pakketype. Finn side-view hvit LED eller kjop originalen fra LCSC (C205440) ved restock. Pris her gjelder LTW-670DS.</t>
         </is>
@@ -867,12 +940,16 @@
       <c r="D20" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="10">
+        <f>IFERROR(B20*D20,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>311-1.00MCRCT-ND</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0805FR-071ML</t>
         </is>
@@ -895,12 +972,16 @@
       <c r="D21" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="10">
+        <f>IFERROR(B21*D21,"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>311-100KHRCT-ND</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0603FR-07100KL</t>
         </is>
@@ -923,12 +1004,16 @@
       <c r="D22" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="10">
+        <f>IFERROR(B22*D22,"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>311-732KHRCT-ND</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0603FR-07732KL</t>
         </is>
@@ -951,12 +1036,16 @@
       <c r="D23" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="10">
+        <f>IFERROR(B23*D23,"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>311-4.70KCRCT-ND</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0805FR-074K7L</t>
         </is>
@@ -979,12 +1068,16 @@
       <c r="D24" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="10">
+        <f>IFERROR(B24*D24,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>311-100KCRCT-ND</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0805FR-07100KL</t>
         </is>
@@ -1007,12 +1100,16 @@
       <c r="D25" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="10">
+        <f>IFERROR(B25*D25,"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>311-470CRCT-ND</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0805FR-07470RL</t>
         </is>
@@ -1035,12 +1132,16 @@
       <c r="D26" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="10">
+        <f>IFERROR(B26*D26,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>311-10.0KCRCT-ND</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>v3 change queued: amp ~SD pull-up should become pull-DOWN (boot noise). | Yageo RC0805FR-0710KL</t>
         </is>
@@ -1063,12 +1164,16 @@
       <c r="D27" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="10">
+        <f>IFERROR(B27*D27,"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>311-80.6CRCT-ND</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0805FR-0780R6L - 80.6 ohm E96 (80 ohm finnes ikke i E96; 0,75% avvik)</t>
         </is>
@@ -1091,12 +1196,16 @@
       <c r="D28" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="10">
+        <f>IFERROR(B28*D28,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>311-1.00KCRCT-ND</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Yageo RC0805FR-071KL</t>
         </is>
@@ -1119,12 +1228,16 @@
       <c r="D29" s="10" t="n">
         <v>3.47</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="10">
+        <f>IFERROR(B29*D29,"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1146840</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>EQUIVALENT: C&amp;K PTS645SM43SMTR92 6x6 SMD tact (TS-1187A-B-A-B ikke hos DigiKey); pris per stk</t>
         </is>
@@ -1147,12 +1260,16 @@
       <c r="D30" s="10" t="n">
         <v>22.57</v>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="10">
+        <f>IFERROR(B30*D30,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>296-25430-1-ND</t>
         </is>
       </c>
-      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
     </row>
     <row r="31" ht="16.4" customHeight="1" s="6">
       <c r="A31" s="9" t="inlineStr">
@@ -1171,12 +1288,16 @@
       <c r="D31" s="10" t="n">
         <v>8.1</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="10">
+        <f>IFERROR(B31*D31,"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1727-PRTR5V0U2X,215CT-ND</t>
         </is>
       </c>
-      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
     </row>
     <row r="32" ht="16.4" customHeight="1" s="6">
       <c r="A32" s="9" t="inlineStr">
@@ -1195,12 +1316,16 @@
       <c r="D32" s="10" t="n">
         <v>28.45</v>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="10">
+        <f>IFERROR(B32*D32,"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>4823-NPM1300-QEAA-R7CT-ND</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
     </row>
     <row r="33" ht="16.4" customHeight="1" s="6">
       <c r="A33" s="9" t="inlineStr">
@@ -1219,12 +1344,16 @@
       <c r="D33" s="10" t="n">
         <v>127.31</v>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="10">
+        <f>IFERROR(B33*D33,"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>13278361</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Quectel L86-M33 - lagerfort hos DigiKey</t>
         </is>
@@ -1247,12 +1376,16 @@
       <c r="D34" s="10" t="n">
         <v>24.59</v>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="10">
+        <f>IFERROR(B34*D34,"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2195-RV-3028-C732.768KHZ1PPM-TA-QCCT-ND</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>RV-3028-C7 32.768KHZ 1PPM-TA-QC</t>
         </is>
@@ -1275,12 +1408,16 @@
       <c r="D35" s="10" t="n">
         <v>11.77</v>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="10">
+        <f>IFERROR(B35*D35,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>296-TPS61023DRLRCT-ND</t>
         </is>
       </c>
-      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
     </row>
     <row r="36" ht="16.4" customHeight="1" s="6">
       <c r="A36" s="9" t="inlineStr">
@@ -1299,12 +1436,16 @@
       <c r="D36" s="10" t="n">
         <v>18.71</v>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="10">
+        <f>IFERROR(B36*D36,"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>497-10613-1-ND</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>LIS3DHTR</t>
         </is>
@@ -1327,12 +1468,16 @@
       <c r="D37" s="10" t="n">
         <v>40.61</v>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="10">
+        <f>IFERROR(B37*D37,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>W25Q128JVSIQCT-ND</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Correct part: W25Q128JVSIQ (3.0V). A 1.8V W25Q128FW was fitted by mistake once; do not repeat.</t>
         </is>
@@ -1355,12 +1500,16 @@
       <c r="D38" s="10" t="n">
         <v>1.45</v>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="10">
+        <f>IFERROR(B38*D38,"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>296-11933-1-ND</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>SN74LVC1G17DBVR</t>
         </is>
@@ -1383,12 +1532,16 @@
       <c r="D39" s="10" t="n">
         <v>4.53</v>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="10">
+        <f>IFERROR(B39*D39,"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>IRLML6344TRPBFCT-ND</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>pris per stk</t>
         </is>
@@ -1411,12 +1564,16 @@
       <c r="D40" s="10" t="n">
         <v>16.98</v>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="10">
+        <f>IFERROR(B40*D40,"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>296-45289-1-ND</t>
         </is>
       </c>
-      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
     </row>
     <row r="41" ht="16.4" customHeight="1" s="6">
       <c r="A41" s="9" t="inlineStr">
@@ -1435,12 +1592,16 @@
       <c r="D41" s="10" t="n">
         <v>64.81</v>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="10">
+        <f>IFERROR(B41*D41,"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>ATSAMD51J20A-AUT-ND</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Schematic says SAMD51J19A - FITTED PART IS SAMD51J20A (verified via bossac). Order J20A.</t>
         </is>
@@ -1463,12 +1624,16 @@
       <c r="D42" s="10" t="n">
         <v>25.66</v>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="10">
+        <f>IFERROR(B42*D42,"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>SER4071CT-ND</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>Epson FC-135R 32.7680KA-A3 (= Q13FC1350000500-krystallen under ordrekode)</t>
         </is>
@@ -1481,8 +1646,10 @@
           <t>Sum komponenter (qty x pris, eks. mva, qty-1-priser):</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
-        <v>709.87</v>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13">
+        <f>SUM(E5:E42)</f>
+        <v/>
       </c>
     </row>
     <row r="45">

--- a/HARDWARE/BOM_GNSS_Alarm_Clock_v2_digikey.xlsx
+++ b/HARDWARE/BOM_GNSS_Alarm_Clock_v2_digikey.xlsx
@@ -387,7 +387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55.64" customWidth="1" style="5" min="1" max="1"/>
@@ -413,7 +413,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="6">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1641,19 +1640,87 @@
     </row>
     <row r="43"/>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Sum komponenter (qty x pris, eks. mva, qty-1-priser):</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13">
-        <f>SUM(E5:E42)</f>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Display NV3007 428x142 TFT (modul m/ BL pull-down)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E44" s="10">
+        <f>B44*D44</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Batteri 505060 LiPo 3.7V 2000mAh m/PCM</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E45" s="10">
+        <f>B45*D45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PCB (produksjon)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" s="10">
+        <f>B46*D46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Diverse: skruer, kabler, 3D-print (kabinett)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" s="10">
+        <f>B47*D47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL per klokke (komponenter + display/batteri/PCB/div, eks. mva):</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13">
+        <f>SUM(E5:E47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Priser fra digikey.no 2026-08-16, eks. mva. EQUIVALENT = original ikke lagerfort hos DigiKey.</t>
         </is>
